--- a/experiment/HAT+CNN_2CH_bestx4/Test/results-Manga109/Manga109.xlsx
+++ b/experiment/HAT+CNN_2CH_bestx4/Test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.5</v>
+        <v>28.51</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8227</v>
+        <v>0.8226</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.03</v>
+        <v>31.05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8141</v>
+        <v>0.8142</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.29</v>
+        <v>28.33</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8456</v>
+        <v>0.8459</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.95</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9477</v>
+        <v>0.9479</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.87</v>
+        <v>39.8</v>
       </c>
       <c r="C6" t="n">
         <v>0.9795</v>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.18</v>
+        <v>30.21</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9163</v>
+        <v>0.9164</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.34</v>
+        <v>33.41</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9578</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.17</v>
+        <v>27.21</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8941</v>
+        <v>0.8942</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.88</v>
+        <v>30.87</v>
       </c>
       <c r="C10" t="n">
-        <v>0.929</v>
+        <v>0.9288999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.48</v>
+        <v>29.45</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8968</v>
+        <v>0.8966</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29.8</v>
+        <v>29.77</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9514</v>
+        <v>0.9518</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.12</v>
+        <v>28.18</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8647</v>
+        <v>0.8652</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.48</v>
+        <v>33.65</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9623</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9035</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.66</v>
+        <v>28.68</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9172</v>
+        <v>0.9174</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.73</v>
+        <v>27.75</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9089</v>
+        <v>0.9088000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.96</v>
+        <v>30.97</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9567</v>
+        <v>0.9566</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.64</v>
+        <v>34.72</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.91</v>
+        <v>30.94</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9026</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.8</v>
+        <v>32.85</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9758</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.94</v>
+        <v>31.99</v>
       </c>
       <c r="C22" t="n">
-        <v>0.923</v>
+        <v>0.9226</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9366</v>
+        <v>0.9367</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.23</v>
+        <v>30.28</v>
       </c>
       <c r="C24" t="n">
-        <v>0.913</v>
+        <v>0.9135</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37.37</v>
+        <v>37.41</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.1</v>
+        <v>29.15</v>
       </c>
       <c r="C26" t="n">
-        <v>0.957</v>
+        <v>0.9573</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.04</v>
+        <v>31.13</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9399</v>
+        <v>0.9405</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38.36</v>
+        <v>38.43</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9782</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.45</v>
+        <v>31.44</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9315</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.04</v>
+        <v>33.17</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9587</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.47</v>
+        <v>31.5</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9431</v>
+        <v>0.9432</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>26.74</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9395</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9317</v>
+        <v>0.9322</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.58</v>
+        <v>32.61</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8946</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.64</v>
+        <v>28.69</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7448</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.38</v>
+        <v>26.44</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8702</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.48</v>
+        <v>31.45</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9117</v>
+        <v>0.9112</v>
       </c>
     </row>
     <row r="38">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.67</v>
+        <v>27.69</v>
       </c>
       <c r="C38" t="n">
         <v>0.8639</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35.21</v>
+        <v>35.27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9712</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>34.94</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9626</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28.22</v>
+        <v>28.2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9005</v>
+        <v>0.8999</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30.84</v>
+        <v>31.02</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8678</v>
+        <v>0.8693</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.7</v>
+        <v>32.78</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9156</v>
+        <v>0.9161</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.75</v>
+        <v>20.77</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7433</v>
+        <v>0.7436</v>
       </c>
     </row>
     <row r="45">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35.25</v>
+        <v>35.27</v>
       </c>
       <c r="C45" t="n">
         <v>0.9772</v>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25.12</v>
+        <v>25.17</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9193</v>
+        <v>0.9199000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27.61</v>
+        <v>27.64</v>
       </c>
       <c r="C47" t="n">
-        <v>0.899</v>
+        <v>0.8989</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>34.73</v>
+        <v>34.74</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9535</v>
+        <v>0.9536</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26.87</v>
+        <v>26.81</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8671</v>
+        <v>0.8663</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.77</v>
+        <v>28.8</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9186</v>
+        <v>0.9191</v>
       </c>
     </row>
     <row r="51">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.68</v>
+        <v>26.69</v>
       </c>
       <c r="C51" t="n">
         <v>0.7619</v>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.37</v>
+        <v>30.47</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9472</v>
+        <v>0.9476</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33.28</v>
+        <v>33.36</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9459</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36.38</v>
+        <v>36.42</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9043</v>
+        <v>0.9044</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35.6</v>
+        <v>35.71</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9637</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22.66</v>
+        <v>22.64</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7275</v>
+        <v>0.7249</v>
       </c>
     </row>
     <row r="57">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33.02</v>
+        <v>33.05</v>
       </c>
       <c r="C57" t="n">
         <v>0.9664</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.72</v>
+        <v>31.08</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         <v>31.97</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9458</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.74</v>
+        <v>23.76</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7659</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33.68</v>
+        <v>33.72</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9705</v>
+        <v>0.9707</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9476</v>
+        <v>0.9475</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.95</v>
+        <v>31</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9504</v>
+        <v>0.9507</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.23</v>
+        <v>35.36</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9686</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>34</v>
+        <v>34.01</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9278</v>
+        <v>0.9274</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.14</v>
+        <v>25.2</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9294</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.15</v>
+        <v>32.01</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9388</v>
+        <v>0.9364</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>32.94</v>
+        <v>32.98</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9311</v>
+        <v>0.9314</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9411</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>28.39</v>
+        <v>28.43</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9238</v>
+        <v>0.9242</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>30.97</v>
+        <v>31.04</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9383</v>
+        <v>0.9384</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.88</v>
+        <v>27.87</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7124</v>
+        <v>0.7119</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>34.96</v>
+        <v>35.03</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9593</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>33.85</v>
+        <v>33.94</v>
       </c>
       <c r="C74" t="n">
-        <v>0.951</v>
+        <v>0.9514</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.12</v>
+        <v>28.16</v>
       </c>
       <c r="C75" t="n">
-        <v>0.89</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="76">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29.67</v>
+        <v>29.69</v>
       </c>
       <c r="C76" t="n">
         <v>0.9015</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.29</v>
+        <v>30.28</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9312</v>
+        <v>0.9314</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>30.28</v>
+        <v>30.31</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8815</v>
+        <v>0.8816000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>28.03</v>
+        <v>28.01</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8092</v>
+        <v>0.8091</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>31</v>
+        <v>31.03</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9342</v>
+        <v>0.9345</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>30.96</v>
+        <v>30.99</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9405</v>
+        <v>0.9406</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29.89</v>
+        <v>29.92</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8738</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>31.84</v>
+        <v>31.88</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9036</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9599</v>
+        <v>0.9603</v>
       </c>
     </row>
     <row r="85">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.64</v>
+        <v>27.62</v>
       </c>
       <c r="C85" t="n">
         <v>0.9451000000000001</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.31</v>
+        <v>32.35</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9324</v>
+        <v>0.9321</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>28.53</v>
+        <v>28.55</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8758</v>
+        <v>0.8754999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.76</v>
+        <v>35.81</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9532</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>34.03</v>
+        <v>34.01</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9634</v>
+        <v>0.9633</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30.28</v>
+        <v>30.32</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9233</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.35</v>
+        <v>25.4</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8627</v>
+        <v>0.8633999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28.67</v>
+        <v>28.74</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9126</v>
+        <v>0.9131</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.45</v>
+        <v>27.54</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9492</v>
+        <v>0.9497</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>21.02</v>
+        <v>21.05</v>
       </c>
       <c r="C94" t="n">
-        <v>0.741</v>
+        <v>0.7417</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>33.99</v>
+        <v>34.17</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9554</v>
+        <v>0.9559</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.57</v>
+        <v>26.61</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8838</v>
+        <v>0.8839</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>29.83</v>
+        <v>29.88</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9094</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>32.63</v>
+        <v>32.67</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8771</v>
+        <v>0.8774</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29</v>
+        <v>29.09</v>
       </c>
       <c r="C99" t="n">
-        <v>0.965</v>
+        <v>0.9656</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26</v>
+        <v>26.04</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7639</v>
+        <v>0.7645</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>23.68</v>
+        <v>23.71</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8927</v>
+        <v>0.8933</v>
       </c>
     </row>
     <row r="102">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.32</v>
+        <v>27.33</v>
       </c>
       <c r="C102" t="n">
         <v>0.9028</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>21.62</v>
+        <v>21.95</v>
       </c>
       <c r="C103" t="n">
-        <v>0.771</v>
+        <v>0.7843</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>36.88</v>
+        <v>37.01</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9759</v>
+        <v>0.9762999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>28.71</v>
+        <v>28.79</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9072</v>
+        <v>0.9075</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33.3</v>
+        <v>33.46</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9756</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="107">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>29.61</v>
+        <v>29.62</v>
       </c>
       <c r="C107" t="n">
         <v>0.8878</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>36.41</v>
+        <v>36.63</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9377</v>
+        <v>0.9383</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>31.56</v>
+        <v>31.61</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8621</v>
+        <v>0.8623</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28.54</v>
+        <v>28.76</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9127</v>
+        <v>0.9169</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30.54</v>
+        <v>30.59</v>
       </c>
       <c r="C111" t="n">
-        <v>0.9097</v>
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
